--- a/output/pdf_financials_xlsx/PWRO.xlsx
+++ b/output/pdf_financials_xlsx/PWRO.xlsx
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000224</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>-0.149756</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.6772629999999999</v>
+        <v>-0.677487</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.669643</v>
@@ -1078,7 +1078,7 @@
         <v>-0.149756</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.6772629999999999</v>
+        <v>-0.677487</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.669643</v>
@@ -1184,19 +1184,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.065761</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.130143</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.000215</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.159544</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.013555</v>
       </c>
     </row>
     <row r="35">
@@ -1228,19 +1228,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.065761</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.130143</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.004275</v>
+        <v>1.00449</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.00285</v>
+        <v>0.162394</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.06535000000000001</v>
+        <v>0.078905</v>
       </c>
     </row>
     <row r="37">
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.101761</v>
+        <v>0.036</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.140103</v>
+        <v>0.00996</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.000215</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.212798</v>
+        <v>0.053254</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.015512</v>
+        <v>0.001957</v>
       </c>
     </row>
     <row r="49">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
